--- a/food-log-template.xlsx
+++ b/food-log-template.xlsx
@@ -7,10 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FoodLog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FoodDatabase" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailySummary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Food Log'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FoodLog'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FoodDatabase'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DailySummary'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Settings'!$A$1:$B$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0034372F"/>
+        <fgColor rgb="00202733"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,21 +142,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FoodLog" displayName="FoodLog" ref="A1:F3" headerRowCount="1">
-  <autoFilter ref="A1:F3"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Date"/>
-    <tableColumn id="2" name="Time"/>
-    <tableColumn id="3" name="Food / Drink"/>
-    <tableColumn id="4" name="Approx. amount"/>
-    <tableColumn id="5" name="Meal"/>
-    <tableColumn id="6" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -442,101 +433,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Food / Drink</t>
+          <t>time</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Approx. amount</t>
+          <t>meal</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Meal</t>
+          <t>food</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>servings</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>calories</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>createdAt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>example-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Egg, whole</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2 eggs</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>144</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Example row - delete me</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>serving</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>calories</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>meal</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chicken rice</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Oats with milk</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1 bowl</t>
-        </is>
+          <t>150 g chicken + 1 cup cooked rice</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Example row — replace or delete</t>
+          <t>Meal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>Chicken breast, cooked</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Chicken and rice</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>150 g chicken + 1 cup rice</t>
-        </is>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>165</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -545,15 +667,500 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Example row — replace or delete</t>
+          <t>Protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Egg, whole</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1 large egg</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Roti</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1 medium roti</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>120</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Roti sabji</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2 rotis + 1 bowl sabji</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>420</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rice, cooked</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>205</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1 bowl</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>180</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oats with milk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>50 g oats + 200 ml milk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>330</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Curd</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>150 g</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1 medium</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>105</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Burger</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1 regular burger</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>550</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fast food</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2 medium slices</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>560</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fast food</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1 serving</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Coffee with milk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>80</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tea with milk and sugar</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Drink</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>calories</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>calorieGoal</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>proteinGoal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>calorieGoalHit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>proteinGoalHit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bothGoalsHit</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>calorieGoal</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>proteinGoal</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>